--- a/module_diff-in-catelog.xlsx
+++ b/module_diff-in-catelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiajin.yan/github_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF633848-12CD-2F40-94A7-AB7CED67BCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCDD32D-7A73-9C41-BBBE-C63A9EBB39D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="34200" windowHeight="20080" xr2:uid="{623F9B81-7EB6-EE49-A7DE-A9A2F519086A}"/>
   </bookViews>
@@ -111,13 +111,13 @@
     <t>Upper 95%CI in Diff %</t>
   </si>
   <si>
-    <t>Put the numbers in Orange and Get the numbers in Grey</t>
-  </si>
-  <si>
     <t>Instruction:</t>
   </si>
   <si>
-    <t>Manual</t>
+    <t>Replace the numbers in Orange and Get the numbers in Light Grey</t>
+  </si>
+  <si>
+    <t>MANUAL</t>
   </si>
 </sst>
 </file>
@@ -163,7 +163,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,24 +178,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -218,49 +212,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -275,45 +232,32 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -331,10 +275,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -657,49 +597,50 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10">
+      <c r="C1" s="9">
         <v>0</v>
       </c>
-      <c r="D1" s="10">
+      <c r="D1" s="9">
         <v>1</v>
       </c>
-      <c r="E1" s="10">
+      <c r="E1" s="9">
         <v>2</v>
       </c>
-      <c r="F1" s="10">
+      <c r="F1" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="8"/>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="7"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="3" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="11">
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -717,63 +658,60 @@
       <c r="F3" s="3">
         <v>6010</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-    </row>
-    <row r="4" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
+      <c r="H3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.70183030000000002</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>0.14608989999999999</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>9.9334400000000003E-2</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>5.2745399999999998E-2</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-    </row>
-    <row r="5" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
+      <c r="H4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+    </row>
+    <row r="5" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.45749250000000002</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>0.35322569999999998</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>0.2991354</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>0.2235434</v>
       </c>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -781,8 +719,8 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="11">
+    <row r="7" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="10">
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -801,43 +739,43 @@
         <v>60038</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
+    <row r="8" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>0.73175319999999999</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>0.1231387</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>0.10744860000000001</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>3.7659499999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
+    <row r="9" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="10"/>
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>0.44305050000000001</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>0.32859909999999998</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>0.3096853</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>0.19037290000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -845,125 +783,126 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="13"/>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <f>C8-C4</f>
         <v>2.9922899999999975E-2</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="12">
         <f>D8-D4</f>
         <v>-2.2951199999999991E-2</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="12">
         <f>E8-E4</f>
         <v>8.114200000000002E-3</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="12">
         <f>F8-F4</f>
         <v>-1.5085899999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="6">
+      <c r="B12" s="13"/>
+      <c r="C12" s="12">
         <f>SQRT((C5*C5/C3) + (C9*C9/C7))</f>
         <v>6.1720888704697744E-3</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="12">
         <f>SQRT((D5*D5/D3) + (D9*D9/D7))</f>
         <v>4.749591147864201E-3</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="12">
         <f>SQRT((E5*E5/E3) + (E9*E9/E7))</f>
         <v>4.0603269039247896E-3</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="12">
         <f>SQRT((F5*F5/F3) + (F9*F9/F7))</f>
         <v>2.9863688770316679E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="6">
+      <c r="B13" s="13"/>
+      <c r="C13" s="12">
         <f xml:space="preserve"> 1.96*C12</f>
         <v>1.2097294186120757E-2</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="12">
         <f xml:space="preserve"> 1.96*D12</f>
         <v>9.3091986498138341E-3</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="12">
         <f xml:space="preserve"> 1.96*E12</f>
         <v>7.9582407316925868E-3</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="12">
         <f>1.96*F12</f>
         <v>5.8532829989820685E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="13"/>
-      <c r="C14" s="6">
+      <c r="C14" s="12">
         <f>C11-C13</f>
         <v>1.7825605813879215E-2</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="12">
         <f>D11-D13</f>
         <v>-3.2260398649813823E-2</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="12">
         <f>E11-E13</f>
         <v>1.5595926830741513E-4</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="12">
         <f>F11-F13</f>
         <v>-2.0939182998982068E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="13"/>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <f>C11+C13</f>
         <v>4.2020194186120734E-2</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="12">
         <f>D11+D13</f>
         <v>-1.3642001350186157E-2</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="12">
         <f>E11+E13</f>
         <v>1.6072440731692589E-2</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="12">
         <f>F11+F13</f>
         <v>-9.2326170010179308E-3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="H3:L3"/>
+  <mergeCells count="8">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="H3:M3"/>
+    <mergeCell ref="H2:M2"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
